--- a/data/trans_orig/P64D$andando_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según cómo se desplaza desde su casa al centro de trabajo/estudios, mediante, al menos, una de las opciones (multirrespuesta) en 2023</t>
+          <t>Población según cómo se desplaza desde su casa al centro de trabajo/estudios, mediante, al menos, una de las opciones (multirrespuesta) en 2023 (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42892</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>30656</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50462</t>
+          <t>49463</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57058</t>
+          <t>54756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85554</t>
+          <t>85588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143017</t>
+          <t>142569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>170413</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98121</t>
+          <t>98036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116420</t>
+          <t>116675</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251391</t>
+          <t>248246</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>282077</t>
+          <t>283545</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16251</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,62 +1217,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3973</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4013</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28168</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35544</t>
+          <t>35075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70474</t>
+          <t>69544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59584</t>
+          <t>59266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79763</t>
+          <t>79555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119910</t>
+          <t>119749</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>172362</t>
+          <t>174523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>207790</t>
+          <t>208705</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111986</t>
+          <t>110549</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131738</t>
+          <t>131893</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>294137</t>
+          <t>294371</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>335066</t>
+          <t>334009</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>24744</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>20516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36929</t>
+          <t>35435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13272</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18151</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>318</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48828</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>41430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59385</t>
+          <t>60454</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73590</t>
+          <t>72724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102731</t>
+          <t>102226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111410</t>
+          <t>111925</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129642</t>
+          <t>130550</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63453</t>
+          <t>64846</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81805</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>181634</t>
+          <t>180340</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>208977</t>
+          <t>207541</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>19751</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48748</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24220</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88136</t>
+          <t>84774</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48420</t>
+          <t>51773</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119996</t>
+          <t>122108</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>176576</t>
+          <t>181285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>227058</t>
+          <t>219456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100881</t>
+          <t>98656</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129704</t>
+          <t>129264</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49891</t>
+          <t>44450</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>182976</t>
+          <t>181026</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>134963</t>
+          <t>136193</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>299756</t>
+          <t>298725</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,09%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22642</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24342</t>
+          <t>23935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -3228,97 +3228,97 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2547</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2434</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2486</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28292</t>
+          <t>28884</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>34605</t>
+          <t>35051</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>40732</t>
+          <t>41204</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58956</t>
+          <t>59208</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54130</t>
+          <t>54625</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68642</t>
+          <t>68481</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>100297</t>
+          <t>100821</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>124206</t>
+          <t>123686</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>763</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>81842</t>
+          <t>82173</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>97171</t>
+          <t>97651</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>75465</t>
+          <t>76111</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>88329</t>
+          <t>88080</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>162478</t>
+          <t>161636</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>181881</t>
+          <t>181333</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>303</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3910,97 +3910,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>49137</t>
+          <t>49471</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>38490</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>54468</t>
+          <t>54008</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>73588</t>
+          <t>73084</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>98923</t>
+          <t>96964</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,62 +4288,62 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>1720</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>6088</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>100532</t>
+          <t>100520</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>117504</t>
+          <t>118089</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>48316</t>
+          <t>48141</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>62694</t>
+          <t>62837</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>152861</t>
+          <t>154155</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>175696</t>
+          <t>175802</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>786</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>163</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>732</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -4705,97 +4705,97 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>1661</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>1491</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>45336</t>
+          <t>44909</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>61458</t>
+          <t>60922</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>87843</t>
+          <t>87417</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>87890</t>
+          <t>88433</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>124362</t>
+          <t>124447</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,82 +4950,82 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3983</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>6886</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2929</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>15709</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>1139</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>4013</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>6886</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>2730</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>16705</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>255828</t>
+          <t>253708</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>286169</t>
+          <t>286617</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>188762</t>
+          <t>189106</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>218373</t>
+          <t>219429</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>450840</t>
+          <t>451942</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>495797</t>
+          <t>499062</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,86%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>31859</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>20288</t>
+          <t>20939</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>39286</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>35507</t>
+          <t>36031</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>62644</t>
+          <t>61367</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5387,12 +5387,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>29547</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>30313</t>
+          <t>31156</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>56438</t>
+          <t>57267</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>41217</t>
+          <t>38537</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>192561</t>
+          <t>187733</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>108886</t>
+          <t>109087</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>139460</t>
+          <t>138691</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>105616</t>
+          <t>111547</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>334133</t>
+          <t>332582</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>19513</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>24349</t>
+          <t>23931</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>352910</t>
+          <t>356843</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>567357</t>
+          <t>574362</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>94436</t>
+          <t>93784</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>122933</t>
+          <t>121831</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>445142</t>
+          <t>443591</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>757907</t>
+          <t>744134</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>27631</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>141721</t>
+          <t>140442</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>66441</t>
+          <t>66499</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>96252</t>
+          <t>96085</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>67624</t>
+          <t>77805</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>228238</t>
+          <t>229459</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>766</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>127</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>41395</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>25423</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>61223</t>
+          <t>59690</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>256105</t>
+          <t>255714</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>453789</t>
+          <t>451392</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>418556</t>
+          <t>423386</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>546259</t>
+          <t>541374</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>676360</t>
+          <t>691675</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>977176</t>
+          <t>977130</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>301237</t>
+          <t>299486</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>31386</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>398185</t>
+          <t>377216</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1457763</t>
+          <t>1453831</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1673040</t>
+          <t>1670403</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>738808</t>
+          <t>735063</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>939288</t>
+          <t>936876</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>2249815</t>
+          <t>2257817</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2625071</t>
+          <t>2597394</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>83786</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>158391</t>
+          <t>158237</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>122483</t>
+          <t>119889</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>177543</t>
+          <t>174491</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>213515</t>
+          <t>217072</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>319655</t>
+          <t>317880</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>27537</t>
+          <t>27774</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>15689</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>37855</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -6751,12 +6751,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>48465</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>97633</t>
+          <t>99132</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>38912</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>66157</t>
+          <t>66794</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>96243</t>
+          <t>95297</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>151993</t>
+          <t>152098</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">

--- a/data/trans_orig/P64D$andando_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>33885</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20719</t>
+          <t>23704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44505</t>
+          <t>47853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30656</t>
+          <t>33268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49463</t>
+          <t>50588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70341</t>
+          <t>75255</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54756</t>
+          <t>60837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85588</t>
+          <t>90719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>160319</t>
+          <t>163754</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>142569</t>
+          <t>149113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>170413</t>
+          <t>175044</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>108581</t>
+          <t>115000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98036</t>
+          <t>105155</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116675</t>
+          <t>123031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>268901</t>
+          <t>278753</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>248246</t>
+          <t>262801</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>283545</t>
+          <t>293860</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -1064,102 +1064,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4139</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1552</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8629</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>11141</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>6465</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>18101</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4029</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1442</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9834</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>12064</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>6295</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>20771</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28677</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>49981</t>
+          <t>54276</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35075</t>
+          <t>35694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69544</t>
+          <t>71898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48658</t>
+          <t>52739</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>42882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59266</t>
+          <t>64221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>98639</t>
+          <t>107015</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79555</t>
+          <t>88696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119749</t>
+          <t>128287</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>193389</t>
+          <t>200656</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>174523</t>
+          <t>182011</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>208705</t>
+          <t>216408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>122419</t>
+          <t>124587</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110549</t>
+          <t>112974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131893</t>
+          <t>134405</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>315809</t>
+          <t>325243</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>294371</t>
+          <t>304566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>334009</t>
+          <t>343085</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>25456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20516</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35435</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17384</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11534</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36679</t>
+          <t>36281</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47934</t>
+          <t>46796</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50176</t>
+          <t>51890</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41430</t>
+          <t>41953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60454</t>
+          <t>61253</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>86855</t>
+          <t>88171</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72724</t>
+          <t>75369</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102226</t>
+          <t>102949</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>121852</t>
+          <t>122556</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111925</t>
+          <t>112742</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130550</t>
+          <t>130365</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73214</t>
+          <t>73302</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64846</t>
+          <t>63782</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83714</t>
+          <t>81714</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>195065</t>
+          <t>195857</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>180340</t>
+          <t>180549</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>207541</t>
+          <t>207038</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19751</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>22736</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2664,92 +2664,92 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1895</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5785</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>4055</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>9405</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>5236</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>4039</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>9192</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35854</t>
+          <t>44980</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>31477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52026</t>
+          <t>63697</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>61211</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>49651</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84774</t>
+          <t>75086</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>89719</t>
+          <t>106191</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51773</t>
+          <t>87678</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122108</t>
+          <t>127648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>31812</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>70358</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>181285</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>72934</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>219456</t>
+          <t>29379</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>116029</t>
+          <t>140391</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>98656</t>
+          <t>118373</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129264</t>
+          <t>156810</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>125096</t>
+          <t>108150</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44450</t>
+          <t>93584</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>181026</t>
+          <t>121447</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>241125</t>
+          <t>248542</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>136193</t>
+          <t>225995</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>298725</t>
+          <t>271014</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>24885</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>30471</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11546</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>21780</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>35051</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>50216</t>
+          <t>58734</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41204</t>
+          <t>49300</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59208</t>
+          <t>69175</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>61878</t>
+          <t>68873</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54625</t>
+          <t>60340</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68481</t>
+          <t>76675</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>112094</t>
+          <t>127607</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>100821</t>
+          <t>115327</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>123686</t>
+          <t>141264</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>749</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>440</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>104329</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>82173</t>
+          <t>94572</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>97651</t>
+          <t>112618</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>82351</t>
+          <t>91038</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>83485</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>88080</t>
+          <t>97462</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>172571</t>
+          <t>195368</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>161636</t>
+          <t>184154</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>181333</t>
+          <t>205353</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>478</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>11324</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>38928</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>29033</t>
+          <t>29709</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>49471</t>
+          <t>49140</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>38490</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>54008</t>
+          <t>55315</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>85095</t>
+          <t>86470</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>73084</t>
+          <t>74771</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>96964</t>
+          <t>99817</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>109659</t>
+          <t>109830</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>100520</t>
+          <t>100072</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>118089</t>
+          <t>118046</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>55839</t>
+          <t>55956</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>48141</t>
+          <t>48395</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>62837</t>
+          <t>63046</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>165498</t>
+          <t>165786</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>154155</t>
+          <t>155087</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>175802</t>
+          <t>177105</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>880</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>31948</t>
+          <t>39044</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>44909</t>
+          <t>53260</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>73081</t>
+          <t>90429</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>60922</t>
+          <t>76181</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>87417</t>
+          <t>105137</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>105029</t>
+          <t>129472</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>88433</t>
+          <t>109100</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>124447</t>
+          <t>151194</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -4930,102 +4930,102 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>2861</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>6733</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>9754</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>21335</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>1139</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>3983</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>6886</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>2929</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>15709</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>271557</t>
+          <t>306744</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>253708</t>
+          <t>288202</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>286617</t>
+          <t>323939</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>204686</t>
+          <t>232525</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>189106</t>
+          <t>214216</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>219429</t>
+          <t>248768</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>476243</t>
+          <t>539269</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>451942</t>
+          <t>512179</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>499062</t>
+          <t>563383</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>17042</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>42469</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>27983</t>
+          <t>35947</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>20939</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>39286</t>
+          <t>48921</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>46528</t>
+          <t>63495</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>36031</t>
+          <t>46837</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>61367</t>
+          <t>79364</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>17355</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>23528</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -5382,32 +5382,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>19863</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>34549</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5417,32 +5417,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>30623</t>
+          <t>37439</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5452,32 +5452,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>55670</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>57267</t>
+          <t>72903</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>109707</t>
+          <t>133197</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>112012</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>187733</t>
+          <t>154965</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>124464</t>
+          <t>140876</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>109087</t>
+          <t>123382</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>138691</t>
+          <t>155989</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>234171</t>
+          <t>274073</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>111547</t>
+          <t>247310</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>332582</t>
+          <t>302517</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>18663</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>27090</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>468300</t>
+          <t>259746</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>356843</t>
+          <t>237176</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>574362</t>
+          <t>280958</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>107623</t>
+          <t>119891</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>93784</t>
+          <t>104691</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>121831</t>
+          <t>137438</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>575923</t>
+          <t>379637</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>443591</t>
+          <t>351182</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>744134</t>
+          <t>407914</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>80227</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>27631</t>
+          <t>82577</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>140442</t>
+          <t>119604</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>80237</t>
+          <t>92858</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>66499</t>
+          <t>77890</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>96085</t>
+          <t>109567</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>160464</t>
+          <t>192858</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>77805</t>
+          <t>168578</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>229459</t>
+          <t>215596</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>0,01%</t>
-        </is>
-      </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -6064,32 +6064,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>22515</t>
+          <t>25816</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>41395</t>
+          <t>38133</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6099,32 +6099,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>17115</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6134,32 +6134,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>39630</t>
+          <t>46808</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>59690</t>
+          <t>61739</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>384014</t>
+          <t>439326</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>255714</t>
+          <t>398335</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>451392</t>
+          <t>480334</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>554929</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>423386</t>
+          <t>521053</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>541374</t>
+          <t>587603</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>881942</t>
+          <t>994255</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>691675</t>
+          <t>940498</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>977130</t>
+          <t>1043525</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>15077</t>
+          <t>24122</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>299486</t>
+          <t>24974</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>55245</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>31386</t>
+          <t>40842</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>377216</t>
+          <t>76760</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1531325</t>
+          <t>1408006</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1453831</t>
+          <t>1363077</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1670403</t>
+          <t>1449760</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>879809</t>
+          <t>920448</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>735063</t>
+          <t>884410</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>936876</t>
+          <t>953875</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>2411135</t>
+          <t>2328455</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>2257817</t>
+          <t>2271399</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2597394</t>
+          <t>2384275</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>80741</t>
+          <t>132684</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>158237</t>
+          <t>189371</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>148643</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>119889</t>
+          <t>149700</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>174491</t>
+          <t>195560</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>276625</t>
+          <t>331335</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>217072</t>
+          <t>294712</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>317880</t>
+          <t>366744</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>16711</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6746,32 +6746,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>48465</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>99132</t>
+          <t>108552</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6781,32 +6781,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>40003</t>
+          <t>49386</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>66794</t>
+          <t>77749</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6816,32 +6816,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>125623</t>
+          <t>148852</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>95297</t>
+          <t>126351</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>152098</t>
+          <t>177170</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
           <t>3,67%</t>
         </is>
       </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64D$andando_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Provincia-trans_orig.xlsx
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>163754</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>149113</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175044</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>115000</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105155</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123031</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>278753</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>262801</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>293860</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1054,112 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1167,112 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>169</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>163754</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>175044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>196</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115000</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>365</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>278753</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>262801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>293860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -1280,112 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>18101</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1623,112 +1623,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>200656</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>182011</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>216408</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>124587</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112974</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134405</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>325243</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>304566</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>343085</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1736,112 +1736,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25456</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36262</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1849,112 +1849,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>135</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>200656</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>182011</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>216408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>124587</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>112974</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>134405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>325243</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>304566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19116</t>
+          <t>343085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -1962,112 +1962,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>25456</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13487</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -2305,112 +2305,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>122556</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>112742</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130365</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73302</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63782</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81714</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>195857</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>180549</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>207038</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -2418,112 +2418,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9094</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6909</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>12643</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>7120</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>20534</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22736</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -2531,112 +2531,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>122556</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>112742</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>130365</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73302</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63782</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81714</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>195857</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>180549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>207038</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2679,77 +2679,77 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>22736</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -2987,112 +2987,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140391</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118373</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>156810</t>
+          <t>30471</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>108150</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>93584</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>121447</t>
+          <t>11546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>248542</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>225995</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>271014</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3100,112 +3100,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>15920</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9578</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24885</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3213,112 +3213,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>140391</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118373</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156810</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108150</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93584</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121447</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>189</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>248542</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>225995</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271014</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -3326,112 +3326,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>24885</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3669,112 +3669,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>104329</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>94572</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112618</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>91038</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>83485</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>97462</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>195368</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>184154</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>205353</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -3782,112 +3782,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3895,112 +3895,112 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104329</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94572</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112618</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>182</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91038</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83485</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97462</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>195368</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184154</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205353</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -4008,112 +4008,112 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>478</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -4351,112 +4351,112 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>109830</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>100072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>118046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>55956</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>48395</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>63046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>165786</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>155087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>177105</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4464,77 +4464,77 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>8475</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>4481</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>4357</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -4577,112 +4577,112 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>109830</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>100072</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>118046</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55956</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48395</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63046</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>165786</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>155087</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>177105</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -4690,112 +4690,112 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>4481</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4357</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5033,112 +5033,112 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>306744</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>288202</t>
+          <t>19863</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>323939</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>232525</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>214216</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>248768</t>
+          <t>37439</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>54</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>539269</t>
+          <t>55670</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>512179</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>563383</t>
+          <t>72903</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -5146,112 +5146,112 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>42469</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>35947</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>48921</t>
+          <t>17355</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>63495</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>46837</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>79364</t>
+          <t>23528</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -5259,112 +5259,112 @@
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>247</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>306744</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>288202</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>323939</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>296</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>232525</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>214216</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>248768</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>543</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>539269</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>512179</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>23528</t>
+          <t>563383</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -5372,112 +5372,112 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>19863</t>
+          <t>17042</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>43718</t>
+          <t>42469</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>25022</t>
+          <t>35947</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>37439</t>
+          <t>48921</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>55670</t>
+          <t>63495</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>43576</t>
+          <t>46837</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>72903</t>
+          <t>79364</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -5715,112 +5715,112 @@
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>259746</t>
+          <t>25816</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>237176</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>280958</t>
+          <t>38133</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>119891</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>104691</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>137438</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>50</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>379637</t>
+          <t>46808</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>351182</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>407914</t>
+          <t>61739</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -5828,112 +5828,112 @@
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>82577</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>119604</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>92858</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>77890</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>109567</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>192858</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>168578</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>215596</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -5941,112 +5941,112 @@
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>259746</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>237176</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>280958</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>146</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>119891</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104691</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>137438</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>371</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>379637</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>351182</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>407914</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -6054,112 +6054,112 @@
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>82577</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>38133</t>
+          <t>119604</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>92858</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>77890</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>109567</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>194</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>46808</t>
+          <t>192858</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>168578</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>61739</t>
+          <t>215596</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -6397,112 +6397,112 @@
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1408006</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1363077</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1449760</t>
+          <t>108552</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>920448</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>884410</t>
+          <t>49386</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>953875</t>
+          <t>77749</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>152</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>2328455</t>
+          <t>148852</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>2271399</t>
+          <t>126351</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2384275</t>
+          <t>177170</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -6510,112 +6510,112 @@
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>158560</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>132684</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>189371</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>172774</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>149700</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>195560</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>331335</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>294712</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6623,112 +6623,112 @@
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>1408006</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>1363077</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>33169</t>
+          <t>1449760</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>920448</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>884410</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>953875</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>2328455</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>2271399</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>2384275</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -6736,112 +6736,112 @@
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>86023</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>67045</t>
+          <t>132684</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>108552</t>
+          <t>189371</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>62829</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>49386</t>
+          <t>149700</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>77749</t>
+          <t>195560</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>340</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>148852</t>
+          <t>331335</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>126351</t>
+          <t>294712</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>177170</t>
+          <t>366744</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
